--- a/artfynd/A 50034-2025 artfynd.xlsx
+++ b/artfynd/A 50034-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100739217</v>
+        <v>100739185</v>
       </c>
       <c r="B2" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526961.6431339518</v>
+        <v>527120</v>
       </c>
       <c r="R2" t="n">
-        <v>6484938.065007705</v>
+        <v>6485042</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2021-09-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Staffan Roos</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -791,19 +776,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100739185</v>
+        <v>100739208</v>
       </c>
       <c r="B3" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527120.5997654478</v>
+        <v>527137</v>
       </c>
       <c r="R3" t="n">
-        <v>6485041.582919066</v>
+        <v>6485005</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,19 +844,9 @@
           <t>2021-09-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Staffan Roos</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -907,19 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121379440</v>
+        <v>100739217</v>
       </c>
       <c r="B4" t="n">
-        <v>102425</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -940,24 +905,20 @@
           <t>Huds.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora sjögestad, Ög</t>
+          <t>Stora Sjögestad, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527154</v>
+        <v>526962</v>
       </c>
       <c r="R4" t="n">
-        <v>6484697</v>
+        <v>6484938</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,22 +956,445 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Solcellspark Stora Sjögestad Linköping</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121379440</v>
+      </c>
+      <c r="B5" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stora sjögestad, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>527154</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6484697</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Greensway AB</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Carin von Köhler</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121379464</v>
+      </c>
+      <c r="B6" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stora sjögestad, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>527116</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6484735</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121379466</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stora sjögestad, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>527118</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6484739</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121379468</v>
+      </c>
+      <c r="B8" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stora sjögestad, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>527109</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6484742</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Skyddsvärda träd</t>
         </is>

--- a/artfynd/A 50034-2025 artfynd.xlsx
+++ b/artfynd/A 50034-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Solcellspark Stora Sjögestad Linköping</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100739185</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Solcellspark Stora Sjögestad Linköping</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100739208</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Solcellspark Stora Sjögestad Linköping</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100739217</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121379440</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121379464</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121379466</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,8 +1434,22 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121379468</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>